--- a/TestFiles-prod-sanity/TransferSheets/[MLB New]EditThis[TransferAgent].xlsx
+++ b/TestFiles-prod-sanity/TransferSheets/[MLB New]EditThis[TransferAgent].xlsx
@@ -88,7 +88,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>TRAN001-A00</t>
+    <t>TRAN001-A00-1790775240465-1790779561945-1790779714126</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
@@ -154,9 +154,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -498,256 +497,236 @@
   <dimension ref="A1:T5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.14785714285714" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.433571428571426" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.147857142857141" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.576428571428572" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.719285714285714" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="9" max="9" width="23.576428571428572" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.576428571428572" style="3" customWidth="1"/>
-    <col min="12" max="12" width="13.576428571428572" style="2" customWidth="1"/>
-    <col min="13" max="13" width="13.576428571428572" style="4" customWidth="1"/>
-    <col min="14" max="14" width="13.576428571428572" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.576428571428572" style="4" customWidth="1"/>
-    <col min="16" max="16" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.576428571428572" style="3" customWidth="1"/>
-    <col min="18" max="19" width="13.576428571428572" style="1" customWidth="1"/>
-    <col min="20" max="20" width="13.576428571428572" style="2" customWidth="1"/>
+    <col min="1" max="1" width="18.14785714285714" customWidth="1"/>
+    <col min="2" max="2" width="18.433571428571426" customWidth="1"/>
+    <col min="3" max="3" width="14.147857142857141" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.576428571428572" customWidth="1"/>
+    <col min="5" max="5" width="13.576428571428572" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.576428571428572" customWidth="1"/>
+    <col min="7" max="7" width="22.719285714285714" customWidth="1"/>
+    <col min="8" max="8" width="13.576428571428572" customWidth="1"/>
+    <col min="9" max="9" width="23.576428571428572" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.576428571428572" customWidth="1"/>
+    <col min="11" max="11" width="13.576428571428572" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.576428571428572" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.576428571428572" style="3" customWidth="1"/>
+    <col min="14" max="14" width="13.576428571428572" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.576428571428572" style="3" customWidth="1"/>
+    <col min="16" max="16" width="13.576428571428572" customWidth="1"/>
+    <col min="17" max="17" width="13.576428571428572" style="2" customWidth="1"/>
+    <col min="18" max="19" width="13.576428571428572" customWidth="1"/>
+    <col min="20" max="20" width="13.576428571428572" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>120876543</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="8">
         <v>1</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="9">
         <v>46023</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="9">
         <v>46023</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="8">
         <v>1</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <v>54.9</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="8">
         <v>0</v>
       </c>
-      <c r="O2" s="11">
+      <c r="O2" s="10">
         <v>48.31</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="9">
         <v>46024</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="T2" s="9">
+      <c r="T2" s="8">
         <v>549</v>
       </c>
     </row>
     <row r="3" ht="19.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="8">
         <v>120876543</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>1</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <v>46023</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="9">
         <v>46023</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="8">
         <v>1</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="10">
         <v>54.9</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3" s="8">
         <v>0</v>
       </c>
-      <c r="O3" s="11">
+      <c r="O3" s="10">
         <v>48.31</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="Q3" s="9">
         <v>46024</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="T3" s="9">
+      <c r="T3" s="8">
         <v>549</v>
       </c>
     </row>
-    <row r="4" ht="19.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="9"/>
+    <row r="4" ht="19.5" customHeight="1" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="I4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="10"/>
+      <c r="Q4" s="6"/>
+      <c r="T4" s="8"/>
     </row>
-    <row r="5" ht="19.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="9"/>
+    <row r="5" ht="19.5" customHeight="1" spans="3:20" x14ac:dyDescent="0.25">
+      <c r="C5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="I5" s="11"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="10"/>
+      <c r="Q5" s="6"/>
+      <c r="T5" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/TestFiles-prod-sanity/TransferSheets/[MLB New]EditThis[TransferAgent].xlsx
+++ b/TestFiles-prod-sanity/TransferSheets/[MLB New]EditThis[TransferAgent].xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Selling agent last name</t>
   </si>
@@ -79,7 +79,10 @@
     <t>Test Transfer</t>
   </si>
   <si>
-    <t>Agent</t>
+    <t>test-Agent</t>
+  </si>
+  <si>
+    <t>120876543</t>
   </si>
   <si>
     <t>232 E KING ST2 , ,, MALVERN, PA, 19355</t>
@@ -88,7 +91,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>TRAN001-A00-1790775240465-1790779561945-1790779714126</t>
+    <t>TRAN001B157132</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
@@ -154,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -185,9 +188,6 @@
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -494,7 +494,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.14785714285714" customWidth="1"/>
@@ -587,29 +587,29 @@
       <c r="B2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="8">
-        <v>120876543</v>
+      <c r="C2" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="8">
         <v>1</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="9">
         <v>46023</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="9">
         <v>46023</v>
@@ -627,106 +627,20 @@
         <v>48.31</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q2" s="9">
-        <v>46024</v>
+        <v>46032</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T2" s="8">
         <v>549</v>
       </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="8">
-        <v>120876543</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="8">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="9">
-        <v>46023</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="9">
-        <v>46023</v>
-      </c>
-      <c r="L3" s="8">
-        <v>1</v>
-      </c>
-      <c r="M3" s="10">
-        <v>54.9</v>
-      </c>
-      <c r="N3" s="8">
-        <v>0</v>
-      </c>
-      <c r="O3" s="10">
-        <v>48.31</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="9">
-        <v>46024</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" s="8">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="4" ht="19.5" customHeight="1" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="I4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="10"/>
-      <c r="Q4" s="6"/>
-      <c r="T4" s="8"/>
-    </row>
-    <row r="5" ht="19.5" customHeight="1" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="I5" s="11"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="10"/>
-      <c r="Q5" s="6"/>
-      <c r="T5" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
